--- a/docs/Sand-Creek-Cattle-Herd-Template.xlsx
+++ b/docs/Sand-Creek-Cattle-Herd-Template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="61">
   <si>
     <t>Tag</t>
   </si>
@@ -56,6 +56,33 @@
     <t>Semen/Sire</t>
   </si>
   <si>
+    <t>Birth Wt</t>
+  </si>
+  <si>
+    <t>Weaning Date</t>
+  </si>
+  <si>
+    <t>Weaning Wt</t>
+  </si>
+  <si>
+    <t>Adj Weaning Wt</t>
+  </si>
+  <si>
+    <t>Daily Gain</t>
+  </si>
+  <si>
+    <t>Herd Index</t>
+  </si>
+  <si>
+    <t>Quality Score</t>
+  </si>
+  <si>
+    <t>Yearling Wt</t>
+  </si>
+  <si>
+    <t>Yearling Gain</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -126,6 +153,24 @@
   </si>
   <si>
     <t>AI sire / semen name or code.</t>
+  </si>
+  <si>
+    <t>Birth weight (lb).</t>
+  </si>
+  <si>
+    <t>Weaning weight (lb).</t>
+  </si>
+  <si>
+    <t>Adjusted (205-day) weaning weight.</t>
+  </si>
+  <si>
+    <t>Average daily gain (ADG).</t>
+  </si>
+  <si>
+    <t>e.g. 15.5 or Choice.</t>
+  </si>
+  <si>
+    <t>Remarks (health, sale info, disposition…).</t>
   </si>
   <si>
     <t>Bulls</t>
@@ -543,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O600"/>
+  <dimension ref="A1:X600"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -559,10 +604,17 @@
     <col min="12" max="12" width="16" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="28" customWidth="1"/>
+    <col min="16" max="16" width="13" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
+    <col min="18" max="18" width="13" customWidth="1"/>
+    <col min="19" max="20" width="10" customWidth="1"/>
+    <col min="21" max="21" width="12" customWidth="1"/>
+    <col min="22" max="22" width="11" customWidth="1"/>
+    <col min="23" max="23" width="12" customWidth="1"/>
+    <col min="24" max="24" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -608,3043 +660,3669 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="P2" s="2"/>
+      <c r="X2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="M3" s="2"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="M5" s="2"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="M6" s="2"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6" s="2"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="M8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="M9" s="2"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="M10" s="2"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="M11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="M12" s="2"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="M13" s="2"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="M14" s="2"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P14" s="2"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="M15" s="2"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P15" s="2"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P16" s="2"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="M18" s="2"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="M19" s="2"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="M20" s="2"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P20" s="2"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="M21" s="2"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P21" s="2"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="M22" s="2"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22" s="2"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="M23" s="2"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P23" s="2"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="M24" s="2"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="M25" s="2"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="M26" s="2"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="M27" s="2"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P27" s="2"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="M28" s="2"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28" s="2"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="M29" s="2"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P29" s="2"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="M30" s="2"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P30" s="2"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="M31" s="2"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P31" s="2"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="M32" s="2"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P32" s="2"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="M33" s="2"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P33" s="2"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="M34" s="2"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P34" s="2"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="M35" s="2"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P35" s="2"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="M36" s="2"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P36" s="2"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="M37" s="2"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P37" s="2"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="M39" s="2"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P39" s="2"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="M40" s="2"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P40" s="2"/>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="M41" s="2"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P41" s="2"/>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="M42" s="2"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P42" s="2"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="M43" s="2"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P43" s="2"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="M44" s="2"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P44" s="2"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="M45" s="2"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P45" s="2"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="M46" s="2"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P46" s="2"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="M47" s="2"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P47" s="2"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="M48" s="2"/>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P48" s="2"/>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="M49" s="2"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P49" s="2"/>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="M50" s="2"/>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P50" s="2"/>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="M51" s="2"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P51" s="2"/>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="M52" s="2"/>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P52" s="2"/>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="M53" s="2"/>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P53" s="2"/>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="M54" s="2"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P54" s="2"/>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="M55" s="2"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P55" s="2"/>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
       <c r="M56" s="2"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P56" s="2"/>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="M57" s="2"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P57" s="2"/>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="M58" s="2"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P58" s="2"/>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="M59" s="2"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P59" s="2"/>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="M60" s="2"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P60" s="2"/>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
       <c r="M61" s="2"/>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P61" s="2"/>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
       <c r="M62" s="2"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P62" s="2"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="M63" s="2"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P63" s="2"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
       <c r="M64" s="2"/>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P64" s="2"/>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
       <c r="M65" s="2"/>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P65" s="2"/>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
       <c r="M66" s="2"/>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P66" s="2"/>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
       <c r="M67" s="2"/>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P67" s="2"/>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
       <c r="M68" s="2"/>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P68" s="2"/>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
       <c r="M69" s="2"/>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P69" s="2"/>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
       <c r="M70" s="2"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P70" s="2"/>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
       <c r="M71" s="2"/>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P71" s="2"/>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
       <c r="M72" s="2"/>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P72" s="2"/>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
       <c r="M73" s="2"/>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P73" s="2"/>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
       <c r="M74" s="2"/>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P74" s="2"/>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
       <c r="M75" s="2"/>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P75" s="2"/>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
       <c r="M76" s="2"/>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P76" s="2"/>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
       <c r="M77" s="2"/>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P77" s="2"/>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
       <c r="M78" s="2"/>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P78" s="2"/>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
       <c r="M79" s="2"/>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P79" s="2"/>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
       <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
       <c r="M81" s="2"/>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P81" s="2"/>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
       <c r="M82" s="2"/>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P82" s="2"/>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
       <c r="M83" s="2"/>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P83" s="2"/>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
       <c r="M84" s="2"/>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P84" s="2"/>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
       <c r="M85" s="2"/>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P85" s="2"/>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
       <c r="M86" s="2"/>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P86" s="2"/>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
       <c r="M87" s="2"/>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P87" s="2"/>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
       <c r="M88" s="2"/>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P88" s="2"/>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
       <c r="M89" s="2"/>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P89" s="2"/>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
       <c r="M90" s="2"/>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P90" s="2"/>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
       <c r="M91" s="2"/>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P91" s="2"/>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
       <c r="M92" s="2"/>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P92" s="2"/>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
       <c r="M93" s="2"/>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P93" s="2"/>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
       <c r="M94" s="2"/>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P94" s="2"/>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
       <c r="M95" s="2"/>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P95" s="2"/>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
       <c r="M96" s="2"/>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P96" s="2"/>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
       <c r="M97" s="2"/>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P97" s="2"/>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
       <c r="M98" s="2"/>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P98" s="2"/>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
       <c r="M99" s="2"/>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P99" s="2"/>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
       <c r="M100" s="2"/>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P100" s="2"/>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
       <c r="M101" s="2"/>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P101" s="2"/>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
       <c r="M102" s="2"/>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P102" s="2"/>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
       <c r="M103" s="2"/>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P103" s="2"/>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
       <c r="M104" s="2"/>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P104" s="2"/>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
       <c r="M105" s="2"/>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P105" s="2"/>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
       <c r="M106" s="2"/>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P106" s="2"/>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
       <c r="M107" s="2"/>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P107" s="2"/>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H108" s="2"/>
       <c r="I108" s="2"/>
       <c r="M108" s="2"/>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P108" s="2"/>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
       <c r="M109" s="2"/>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P109" s="2"/>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
       <c r="M110" s="2"/>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P110" s="2"/>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
       <c r="M111" s="2"/>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P111" s="2"/>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
       <c r="M112" s="2"/>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P112" s="2"/>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
       <c r="M113" s="2"/>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P113" s="2"/>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
       <c r="M114" s="2"/>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P114" s="2"/>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
       <c r="M115" s="2"/>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P115" s="2"/>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
       <c r="M116" s="2"/>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P116" s="2"/>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
       <c r="M117" s="2"/>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P117" s="2"/>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
       <c r="M118" s="2"/>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P118" s="2"/>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
       <c r="M119" s="2"/>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P119" s="2"/>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
       <c r="M120" s="2"/>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P120" s="2"/>
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
       <c r="M121" s="2"/>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P121" s="2"/>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H122" s="2"/>
       <c r="I122" s="2"/>
       <c r="M122" s="2"/>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P122" s="2"/>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
       <c r="M123" s="2"/>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P123" s="2"/>
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H124" s="2"/>
       <c r="I124" s="2"/>
       <c r="M124" s="2"/>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P124" s="2"/>
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H125" s="2"/>
       <c r="I125" s="2"/>
       <c r="M125" s="2"/>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P125" s="2"/>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
       <c r="M126" s="2"/>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P126" s="2"/>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H127" s="2"/>
       <c r="I127" s="2"/>
       <c r="M127" s="2"/>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P127" s="2"/>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
       <c r="M128" s="2"/>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P128" s="2"/>
+    </row>
+    <row r="129" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H129" s="2"/>
       <c r="I129" s="2"/>
       <c r="M129" s="2"/>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P129" s="2"/>
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
       <c r="M130" s="2"/>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P130" s="2"/>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
       <c r="M131" s="2"/>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P131" s="2"/>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
       <c r="M132" s="2"/>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P132" s="2"/>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
       <c r="M133" s="2"/>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P133" s="2"/>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
       <c r="M134" s="2"/>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P134" s="2"/>
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
       <c r="M135" s="2"/>
-    </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P135" s="2"/>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H136" s="2"/>
       <c r="I136" s="2"/>
       <c r="M136" s="2"/>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P136" s="2"/>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H137" s="2"/>
       <c r="I137" s="2"/>
       <c r="M137" s="2"/>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P137" s="2"/>
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H138" s="2"/>
       <c r="I138" s="2"/>
       <c r="M138" s="2"/>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P138" s="2"/>
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H139" s="2"/>
       <c r="I139" s="2"/>
       <c r="M139" s="2"/>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P139" s="2"/>
+    </row>
+    <row r="140" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H140" s="2"/>
       <c r="I140" s="2"/>
       <c r="M140" s="2"/>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P140" s="2"/>
+    </row>
+    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H141" s="2"/>
       <c r="I141" s="2"/>
       <c r="M141" s="2"/>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P141" s="2"/>
+    </row>
+    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H142" s="2"/>
       <c r="I142" s="2"/>
       <c r="M142" s="2"/>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P142" s="2"/>
+    </row>
+    <row r="143" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H143" s="2"/>
       <c r="I143" s="2"/>
       <c r="M143" s="2"/>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P143" s="2"/>
+    </row>
+    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H144" s="2"/>
       <c r="I144" s="2"/>
       <c r="M144" s="2"/>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P144" s="2"/>
+    </row>
+    <row r="145" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H145" s="2"/>
       <c r="I145" s="2"/>
       <c r="M145" s="2"/>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P145" s="2"/>
+    </row>
+    <row r="146" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H146" s="2"/>
       <c r="I146" s="2"/>
       <c r="M146" s="2"/>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P146" s="2"/>
+    </row>
+    <row r="147" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H147" s="2"/>
       <c r="I147" s="2"/>
       <c r="M147" s="2"/>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P147" s="2"/>
+    </row>
+    <row r="148" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H148" s="2"/>
       <c r="I148" s="2"/>
       <c r="M148" s="2"/>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P148" s="2"/>
+    </row>
+    <row r="149" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H149" s="2"/>
       <c r="I149" s="2"/>
       <c r="M149" s="2"/>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P149" s="2"/>
+    </row>
+    <row r="150" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H150" s="2"/>
       <c r="I150" s="2"/>
       <c r="M150" s="2"/>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P150" s="2"/>
+    </row>
+    <row r="151" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H151" s="2"/>
       <c r="I151" s="2"/>
       <c r="M151" s="2"/>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P151" s="2"/>
+    </row>
+    <row r="152" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H152" s="2"/>
       <c r="I152" s="2"/>
       <c r="M152" s="2"/>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P152" s="2"/>
+    </row>
+    <row r="153" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H153" s="2"/>
       <c r="I153" s="2"/>
       <c r="M153" s="2"/>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P153" s="2"/>
+    </row>
+    <row r="154" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H154" s="2"/>
       <c r="I154" s="2"/>
       <c r="M154" s="2"/>
-    </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P154" s="2"/>
+    </row>
+    <row r="155" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
       <c r="M155" s="2"/>
-    </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P155" s="2"/>
+    </row>
+    <row r="156" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H156" s="2"/>
       <c r="I156" s="2"/>
       <c r="M156" s="2"/>
-    </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P156" s="2"/>
+    </row>
+    <row r="157" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H157" s="2"/>
       <c r="I157" s="2"/>
       <c r="M157" s="2"/>
-    </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P157" s="2"/>
+    </row>
+    <row r="158" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H158" s="2"/>
       <c r="I158" s="2"/>
       <c r="M158" s="2"/>
-    </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P158" s="2"/>
+    </row>
+    <row r="159" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H159" s="2"/>
       <c r="I159" s="2"/>
       <c r="M159" s="2"/>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P159" s="2"/>
+    </row>
+    <row r="160" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H160" s="2"/>
       <c r="I160" s="2"/>
       <c r="M160" s="2"/>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P160" s="2"/>
+    </row>
+    <row r="161" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H161" s="2"/>
       <c r="I161" s="2"/>
       <c r="M161" s="2"/>
-    </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P161" s="2"/>
+    </row>
+    <row r="162" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H162" s="2"/>
       <c r="I162" s="2"/>
       <c r="M162" s="2"/>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P162" s="2"/>
+    </row>
+    <row r="163" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
       <c r="M163" s="2"/>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P163" s="2"/>
+    </row>
+    <row r="164" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
       <c r="M164" s="2"/>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P164" s="2"/>
+    </row>
+    <row r="165" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H165" s="2"/>
       <c r="I165" s="2"/>
       <c r="M165" s="2"/>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P165" s="2"/>
+    </row>
+    <row r="166" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H166" s="2"/>
       <c r="I166" s="2"/>
       <c r="M166" s="2"/>
-    </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P166" s="2"/>
+    </row>
+    <row r="167" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
       <c r="M167" s="2"/>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P167" s="2"/>
+    </row>
+    <row r="168" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
       <c r="M168" s="2"/>
-    </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P168" s="2"/>
+    </row>
+    <row r="169" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
       <c r="M169" s="2"/>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P169" s="2"/>
+    </row>
+    <row r="170" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
       <c r="M170" s="2"/>
-    </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P170" s="2"/>
+    </row>
+    <row r="171" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
       <c r="M171" s="2"/>
-    </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P171" s="2"/>
+    </row>
+    <row r="172" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
       <c r="M172" s="2"/>
-    </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P172" s="2"/>
+    </row>
+    <row r="173" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
       <c r="M173" s="2"/>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P173" s="2"/>
+    </row>
+    <row r="174" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
       <c r="M174" s="2"/>
-    </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P174" s="2"/>
+    </row>
+    <row r="175" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
       <c r="M175" s="2"/>
-    </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P175" s="2"/>
+    </row>
+    <row r="176" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H176" s="2"/>
       <c r="I176" s="2"/>
       <c r="M176" s="2"/>
-    </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P176" s="2"/>
+    </row>
+    <row r="177" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H177" s="2"/>
       <c r="I177" s="2"/>
       <c r="M177" s="2"/>
-    </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P177" s="2"/>
+    </row>
+    <row r="178" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H178" s="2"/>
       <c r="I178" s="2"/>
       <c r="M178" s="2"/>
-    </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P178" s="2"/>
+    </row>
+    <row r="179" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
       <c r="M179" s="2"/>
-    </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P179" s="2"/>
+    </row>
+    <row r="180" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H180" s="2"/>
       <c r="I180" s="2"/>
       <c r="M180" s="2"/>
-    </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P180" s="2"/>
+    </row>
+    <row r="181" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H181" s="2"/>
       <c r="I181" s="2"/>
       <c r="M181" s="2"/>
-    </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P181" s="2"/>
+    </row>
+    <row r="182" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H182" s="2"/>
       <c r="I182" s="2"/>
       <c r="M182" s="2"/>
-    </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P182" s="2"/>
+    </row>
+    <row r="183" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H183" s="2"/>
       <c r="I183" s="2"/>
       <c r="M183" s="2"/>
-    </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P183" s="2"/>
+    </row>
+    <row r="184" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H184" s="2"/>
       <c r="I184" s="2"/>
       <c r="M184" s="2"/>
-    </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P184" s="2"/>
+    </row>
+    <row r="185" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H185" s="2"/>
       <c r="I185" s="2"/>
       <c r="M185" s="2"/>
-    </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P185" s="2"/>
+    </row>
+    <row r="186" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H186" s="2"/>
       <c r="I186" s="2"/>
       <c r="M186" s="2"/>
-    </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P186" s="2"/>
+    </row>
+    <row r="187" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>
       <c r="M187" s="2"/>
-    </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P187" s="2"/>
+    </row>
+    <row r="188" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H188" s="2"/>
       <c r="I188" s="2"/>
       <c r="M188" s="2"/>
-    </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P188" s="2"/>
+    </row>
+    <row r="189" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="2"/>
       <c r="M189" s="2"/>
-    </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P189" s="2"/>
+    </row>
+    <row r="190" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H190" s="2"/>
       <c r="I190" s="2"/>
       <c r="M190" s="2"/>
-    </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P190" s="2"/>
+    </row>
+    <row r="191" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H191" s="2"/>
       <c r="I191" s="2"/>
       <c r="M191" s="2"/>
-    </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P191" s="2"/>
+    </row>
+    <row r="192" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
       <c r="M192" s="2"/>
-    </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P192" s="2"/>
+    </row>
+    <row r="193" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H193" s="2"/>
       <c r="I193" s="2"/>
       <c r="M193" s="2"/>
-    </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P193" s="2"/>
+    </row>
+    <row r="194" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
       <c r="M194" s="2"/>
-    </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P194" s="2"/>
+    </row>
+    <row r="195" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H195" s="2"/>
       <c r="I195" s="2"/>
       <c r="M195" s="2"/>
-    </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P195" s="2"/>
+    </row>
+    <row r="196" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H196" s="2"/>
       <c r="I196" s="2"/>
       <c r="M196" s="2"/>
-    </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P196" s="2"/>
+    </row>
+    <row r="197" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H197" s="2"/>
       <c r="I197" s="2"/>
       <c r="M197" s="2"/>
-    </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P197" s="2"/>
+    </row>
+    <row r="198" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H198" s="2"/>
       <c r="I198" s="2"/>
       <c r="M198" s="2"/>
-    </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P198" s="2"/>
+    </row>
+    <row r="199" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
       <c r="M199" s="2"/>
-    </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P199" s="2"/>
+    </row>
+    <row r="200" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>
       <c r="M200" s="2"/>
-    </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P200" s="2"/>
+    </row>
+    <row r="201" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H201" s="2"/>
       <c r="I201" s="2"/>
       <c r="M201" s="2"/>
-    </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P201" s="2"/>
+    </row>
+    <row r="202" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H202" s="2"/>
       <c r="I202" s="2"/>
       <c r="M202" s="2"/>
-    </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P202" s="2"/>
+    </row>
+    <row r="203" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H203" s="2"/>
       <c r="I203" s="2"/>
       <c r="M203" s="2"/>
-    </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P203" s="2"/>
+    </row>
+    <row r="204" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H204" s="2"/>
       <c r="I204" s="2"/>
       <c r="M204" s="2"/>
-    </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P204" s="2"/>
+    </row>
+    <row r="205" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H205" s="2"/>
       <c r="I205" s="2"/>
       <c r="M205" s="2"/>
-    </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P205" s="2"/>
+    </row>
+    <row r="206" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H206" s="2"/>
       <c r="I206" s="2"/>
       <c r="M206" s="2"/>
-    </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P206" s="2"/>
+    </row>
+    <row r="207" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="2"/>
       <c r="M207" s="2"/>
-    </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P207" s="2"/>
+    </row>
+    <row r="208" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H208" s="2"/>
       <c r="I208" s="2"/>
       <c r="M208" s="2"/>
-    </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P208" s="2"/>
+    </row>
+    <row r="209" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H209" s="2"/>
       <c r="I209" s="2"/>
       <c r="M209" s="2"/>
-    </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P209" s="2"/>
+    </row>
+    <row r="210" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H210" s="2"/>
       <c r="I210" s="2"/>
       <c r="M210" s="2"/>
-    </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P210" s="2"/>
+    </row>
+    <row r="211" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H211" s="2"/>
       <c r="I211" s="2"/>
       <c r="M211" s="2"/>
-    </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P211" s="2"/>
+    </row>
+    <row r="212" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H212" s="2"/>
       <c r="I212" s="2"/>
       <c r="M212" s="2"/>
-    </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P212" s="2"/>
+    </row>
+    <row r="213" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H213" s="2"/>
       <c r="I213" s="2"/>
       <c r="M213" s="2"/>
-    </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P213" s="2"/>
+    </row>
+    <row r="214" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H214" s="2"/>
       <c r="I214" s="2"/>
       <c r="M214" s="2"/>
-    </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P214" s="2"/>
+    </row>
+    <row r="215" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H215" s="2"/>
       <c r="I215" s="2"/>
       <c r="M215" s="2"/>
-    </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P215" s="2"/>
+    </row>
+    <row r="216" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H216" s="2"/>
       <c r="I216" s="2"/>
       <c r="M216" s="2"/>
-    </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P216" s="2"/>
+    </row>
+    <row r="217" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H217" s="2"/>
       <c r="I217" s="2"/>
       <c r="M217" s="2"/>
-    </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P217" s="2"/>
+    </row>
+    <row r="218" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H218" s="2"/>
       <c r="I218" s="2"/>
       <c r="M218" s="2"/>
-    </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P218" s="2"/>
+    </row>
+    <row r="219" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H219" s="2"/>
       <c r="I219" s="2"/>
       <c r="M219" s="2"/>
-    </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P219" s="2"/>
+    </row>
+    <row r="220" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H220" s="2"/>
       <c r="I220" s="2"/>
       <c r="M220" s="2"/>
-    </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P220" s="2"/>
+    </row>
+    <row r="221" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H221" s="2"/>
       <c r="I221" s="2"/>
       <c r="M221" s="2"/>
-    </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P221" s="2"/>
+    </row>
+    <row r="222" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H222" s="2"/>
       <c r="I222" s="2"/>
       <c r="M222" s="2"/>
-    </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P222" s="2"/>
+    </row>
+    <row r="223" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H223" s="2"/>
       <c r="I223" s="2"/>
       <c r="M223" s="2"/>
-    </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P223" s="2"/>
+    </row>
+    <row r="224" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H224" s="2"/>
       <c r="I224" s="2"/>
       <c r="M224" s="2"/>
-    </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P224" s="2"/>
+    </row>
+    <row r="225" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H225" s="2"/>
       <c r="I225" s="2"/>
       <c r="M225" s="2"/>
-    </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P225" s="2"/>
+    </row>
+    <row r="226" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H226" s="2"/>
       <c r="I226" s="2"/>
       <c r="M226" s="2"/>
-    </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P226" s="2"/>
+    </row>
+    <row r="227" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H227" s="2"/>
       <c r="I227" s="2"/>
       <c r="M227" s="2"/>
-    </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P227" s="2"/>
+    </row>
+    <row r="228" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H228" s="2"/>
       <c r="I228" s="2"/>
       <c r="M228" s="2"/>
-    </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P228" s="2"/>
+    </row>
+    <row r="229" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H229" s="2"/>
       <c r="I229" s="2"/>
       <c r="M229" s="2"/>
-    </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P229" s="2"/>
+    </row>
+    <row r="230" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H230" s="2"/>
       <c r="I230" s="2"/>
       <c r="M230" s="2"/>
-    </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P230" s="2"/>
+    </row>
+    <row r="231" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H231" s="2"/>
       <c r="I231" s="2"/>
       <c r="M231" s="2"/>
-    </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P231" s="2"/>
+    </row>
+    <row r="232" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H232" s="2"/>
       <c r="I232" s="2"/>
       <c r="M232" s="2"/>
-    </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P232" s="2"/>
+    </row>
+    <row r="233" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H233" s="2"/>
       <c r="I233" s="2"/>
       <c r="M233" s="2"/>
-    </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P233" s="2"/>
+    </row>
+    <row r="234" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H234" s="2"/>
       <c r="I234" s="2"/>
       <c r="M234" s="2"/>
-    </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P234" s="2"/>
+    </row>
+    <row r="235" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H235" s="2"/>
       <c r="I235" s="2"/>
       <c r="M235" s="2"/>
-    </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P235" s="2"/>
+    </row>
+    <row r="236" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H236" s="2"/>
       <c r="I236" s="2"/>
       <c r="M236" s="2"/>
-    </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P236" s="2"/>
+    </row>
+    <row r="237" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H237" s="2"/>
       <c r="I237" s="2"/>
       <c r="M237" s="2"/>
-    </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P237" s="2"/>
+    </row>
+    <row r="238" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H238" s="2"/>
       <c r="I238" s="2"/>
       <c r="M238" s="2"/>
-    </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P238" s="2"/>
+    </row>
+    <row r="239" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="2"/>
       <c r="M239" s="2"/>
-    </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P239" s="2"/>
+    </row>
+    <row r="240" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H240" s="2"/>
       <c r="I240" s="2"/>
       <c r="M240" s="2"/>
-    </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P240" s="2"/>
+    </row>
+    <row r="241" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H241" s="2"/>
       <c r="I241" s="2"/>
       <c r="M241" s="2"/>
-    </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P241" s="2"/>
+    </row>
+    <row r="242" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H242" s="2"/>
       <c r="I242" s="2"/>
       <c r="M242" s="2"/>
-    </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P242" s="2"/>
+    </row>
+    <row r="243" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H243" s="2"/>
       <c r="I243" s="2"/>
       <c r="M243" s="2"/>
-    </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P243" s="2"/>
+    </row>
+    <row r="244" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H244" s="2"/>
       <c r="I244" s="2"/>
       <c r="M244" s="2"/>
-    </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P244" s="2"/>
+    </row>
+    <row r="245" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H245" s="2"/>
       <c r="I245" s="2"/>
       <c r="M245" s="2"/>
-    </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P245" s="2"/>
+    </row>
+    <row r="246" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H246" s="2"/>
       <c r="I246" s="2"/>
       <c r="M246" s="2"/>
-    </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P246" s="2"/>
+    </row>
+    <row r="247" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H247" s="2"/>
       <c r="I247" s="2"/>
       <c r="M247" s="2"/>
-    </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P247" s="2"/>
+    </row>
+    <row r="248" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H248" s="2"/>
       <c r="I248" s="2"/>
       <c r="M248" s="2"/>
-    </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P248" s="2"/>
+    </row>
+    <row r="249" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H249" s="2"/>
       <c r="I249" s="2"/>
       <c r="M249" s="2"/>
-    </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P249" s="2"/>
+    </row>
+    <row r="250" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H250" s="2"/>
       <c r="I250" s="2"/>
       <c r="M250" s="2"/>
-    </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P250" s="2"/>
+    </row>
+    <row r="251" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H251" s="2"/>
       <c r="I251" s="2"/>
       <c r="M251" s="2"/>
-    </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P251" s="2"/>
+    </row>
+    <row r="252" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H252" s="2"/>
       <c r="I252" s="2"/>
       <c r="M252" s="2"/>
-    </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P252" s="2"/>
+    </row>
+    <row r="253" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H253" s="2"/>
       <c r="I253" s="2"/>
       <c r="M253" s="2"/>
-    </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P253" s="2"/>
+    </row>
+    <row r="254" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H254" s="2"/>
       <c r="I254" s="2"/>
       <c r="M254" s="2"/>
-    </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P254" s="2"/>
+    </row>
+    <row r="255" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H255" s="2"/>
       <c r="I255" s="2"/>
       <c r="M255" s="2"/>
-    </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P255" s="2"/>
+    </row>
+    <row r="256" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H256" s="2"/>
       <c r="I256" s="2"/>
       <c r="M256" s="2"/>
-    </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P256" s="2"/>
+    </row>
+    <row r="257" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H257" s="2"/>
       <c r="I257" s="2"/>
       <c r="M257" s="2"/>
-    </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P257" s="2"/>
+    </row>
+    <row r="258" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H258" s="2"/>
       <c r="I258" s="2"/>
       <c r="M258" s="2"/>
-    </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P258" s="2"/>
+    </row>
+    <row r="259" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H259" s="2"/>
       <c r="I259" s="2"/>
       <c r="M259" s="2"/>
-    </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P259" s="2"/>
+    </row>
+    <row r="260" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H260" s="2"/>
       <c r="I260" s="2"/>
       <c r="M260" s="2"/>
-    </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P260" s="2"/>
+    </row>
+    <row r="261" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H261" s="2"/>
       <c r="I261" s="2"/>
       <c r="M261" s="2"/>
-    </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P261" s="2"/>
+    </row>
+    <row r="262" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H262" s="2"/>
       <c r="I262" s="2"/>
       <c r="M262" s="2"/>
-    </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P262" s="2"/>
+    </row>
+    <row r="263" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H263" s="2"/>
       <c r="I263" s="2"/>
       <c r="M263" s="2"/>
-    </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P263" s="2"/>
+    </row>
+    <row r="264" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H264" s="2"/>
       <c r="I264" s="2"/>
       <c r="M264" s="2"/>
-    </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P264" s="2"/>
+    </row>
+    <row r="265" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H265" s="2"/>
       <c r="I265" s="2"/>
       <c r="M265" s="2"/>
-    </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P265" s="2"/>
+    </row>
+    <row r="266" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H266" s="2"/>
       <c r="I266" s="2"/>
       <c r="M266" s="2"/>
-    </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P266" s="2"/>
+    </row>
+    <row r="267" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H267" s="2"/>
       <c r="I267" s="2"/>
       <c r="M267" s="2"/>
-    </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P267" s="2"/>
+    </row>
+    <row r="268" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H268" s="2"/>
       <c r="I268" s="2"/>
       <c r="M268" s="2"/>
-    </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P268" s="2"/>
+    </row>
+    <row r="269" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H269" s="2"/>
       <c r="I269" s="2"/>
       <c r="M269" s="2"/>
-    </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P269" s="2"/>
+    </row>
+    <row r="270" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H270" s="2"/>
       <c r="I270" s="2"/>
       <c r="M270" s="2"/>
-    </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P270" s="2"/>
+    </row>
+    <row r="271" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H271" s="2"/>
       <c r="I271" s="2"/>
       <c r="M271" s="2"/>
-    </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P271" s="2"/>
+    </row>
+    <row r="272" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H272" s="2"/>
       <c r="I272" s="2"/>
       <c r="M272" s="2"/>
-    </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P272" s="2"/>
+    </row>
+    <row r="273" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H273" s="2"/>
       <c r="I273" s="2"/>
       <c r="M273" s="2"/>
-    </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P273" s="2"/>
+    </row>
+    <row r="274" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H274" s="2"/>
       <c r="I274" s="2"/>
       <c r="M274" s="2"/>
-    </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P274" s="2"/>
+    </row>
+    <row r="275" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H275" s="2"/>
       <c r="I275" s="2"/>
       <c r="M275" s="2"/>
-    </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P275" s="2"/>
+    </row>
+    <row r="276" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H276" s="2"/>
       <c r="I276" s="2"/>
       <c r="M276" s="2"/>
-    </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P276" s="2"/>
+    </row>
+    <row r="277" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H277" s="2"/>
       <c r="I277" s="2"/>
       <c r="M277" s="2"/>
-    </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P277" s="2"/>
+    </row>
+    <row r="278" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H278" s="2"/>
       <c r="I278" s="2"/>
       <c r="M278" s="2"/>
-    </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P278" s="2"/>
+    </row>
+    <row r="279" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H279" s="2"/>
       <c r="I279" s="2"/>
       <c r="M279" s="2"/>
-    </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P279" s="2"/>
+    </row>
+    <row r="280" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H280" s="2"/>
       <c r="I280" s="2"/>
       <c r="M280" s="2"/>
-    </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P280" s="2"/>
+    </row>
+    <row r="281" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H281" s="2"/>
       <c r="I281" s="2"/>
       <c r="M281" s="2"/>
-    </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P281" s="2"/>
+    </row>
+    <row r="282" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H282" s="2"/>
       <c r="I282" s="2"/>
       <c r="M282" s="2"/>
-    </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P282" s="2"/>
+    </row>
+    <row r="283" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H283" s="2"/>
       <c r="I283" s="2"/>
       <c r="M283" s="2"/>
-    </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P283" s="2"/>
+    </row>
+    <row r="284" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H284" s="2"/>
       <c r="I284" s="2"/>
       <c r="M284" s="2"/>
-    </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P284" s="2"/>
+    </row>
+    <row r="285" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H285" s="2"/>
       <c r="I285" s="2"/>
       <c r="M285" s="2"/>
-    </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P285" s="2"/>
+    </row>
+    <row r="286" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H286" s="2"/>
       <c r="I286" s="2"/>
       <c r="M286" s="2"/>
-    </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P286" s="2"/>
+    </row>
+    <row r="287" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H287" s="2"/>
       <c r="I287" s="2"/>
       <c r="M287" s="2"/>
-    </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P287" s="2"/>
+    </row>
+    <row r="288" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H288" s="2"/>
       <c r="I288" s="2"/>
       <c r="M288" s="2"/>
-    </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P288" s="2"/>
+    </row>
+    <row r="289" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H289" s="2"/>
       <c r="I289" s="2"/>
       <c r="M289" s="2"/>
-    </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P289" s="2"/>
+    </row>
+    <row r="290" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H290" s="2"/>
       <c r="I290" s="2"/>
       <c r="M290" s="2"/>
-    </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P290" s="2"/>
+    </row>
+    <row r="291" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H291" s="2"/>
       <c r="I291" s="2"/>
       <c r="M291" s="2"/>
-    </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P291" s="2"/>
+    </row>
+    <row r="292" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H292" s="2"/>
       <c r="I292" s="2"/>
       <c r="M292" s="2"/>
-    </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P292" s="2"/>
+    </row>
+    <row r="293" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H293" s="2"/>
       <c r="I293" s="2"/>
       <c r="M293" s="2"/>
-    </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P293" s="2"/>
+    </row>
+    <row r="294" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H294" s="2"/>
       <c r="I294" s="2"/>
       <c r="M294" s="2"/>
-    </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P294" s="2"/>
+    </row>
+    <row r="295" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H295" s="2"/>
       <c r="I295" s="2"/>
       <c r="M295" s="2"/>
-    </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P295" s="2"/>
+    </row>
+    <row r="296" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H296" s="2"/>
       <c r="I296" s="2"/>
       <c r="M296" s="2"/>
-    </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P296" s="2"/>
+    </row>
+    <row r="297" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H297" s="2"/>
       <c r="I297" s="2"/>
       <c r="M297" s="2"/>
-    </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P297" s="2"/>
+    </row>
+    <row r="298" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H298" s="2"/>
       <c r="I298" s="2"/>
       <c r="M298" s="2"/>
-    </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P298" s="2"/>
+    </row>
+    <row r="299" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H299" s="2"/>
       <c r="I299" s="2"/>
       <c r="M299" s="2"/>
-    </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P299" s="2"/>
+    </row>
+    <row r="300" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H300" s="2"/>
       <c r="I300" s="2"/>
       <c r="M300" s="2"/>
-    </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P300" s="2"/>
+    </row>
+    <row r="301" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H301" s="2"/>
       <c r="I301" s="2"/>
       <c r="M301" s="2"/>
-    </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P301" s="2"/>
+    </row>
+    <row r="302" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H302" s="2"/>
       <c r="I302" s="2"/>
       <c r="M302" s="2"/>
-    </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P302" s="2"/>
+    </row>
+    <row r="303" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H303" s="2"/>
       <c r="I303" s="2"/>
       <c r="M303" s="2"/>
-    </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P303" s="2"/>
+    </row>
+    <row r="304" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H304" s="2"/>
       <c r="I304" s="2"/>
       <c r="M304" s="2"/>
-    </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P304" s="2"/>
+    </row>
+    <row r="305" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H305" s="2"/>
       <c r="I305" s="2"/>
       <c r="M305" s="2"/>
-    </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P305" s="2"/>
+    </row>
+    <row r="306" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H306" s="2"/>
       <c r="I306" s="2"/>
       <c r="M306" s="2"/>
-    </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P306" s="2"/>
+    </row>
+    <row r="307" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H307" s="2"/>
       <c r="I307" s="2"/>
       <c r="M307" s="2"/>
-    </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P307" s="2"/>
+    </row>
+    <row r="308" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H308" s="2"/>
       <c r="I308" s="2"/>
       <c r="M308" s="2"/>
-    </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P308" s="2"/>
+    </row>
+    <row r="309" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H309" s="2"/>
       <c r="I309" s="2"/>
       <c r="M309" s="2"/>
-    </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P309" s="2"/>
+    </row>
+    <row r="310" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H310" s="2"/>
       <c r="I310" s="2"/>
       <c r="M310" s="2"/>
-    </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P310" s="2"/>
+    </row>
+    <row r="311" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H311" s="2"/>
       <c r="I311" s="2"/>
       <c r="M311" s="2"/>
-    </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P311" s="2"/>
+    </row>
+    <row r="312" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H312" s="2"/>
       <c r="I312" s="2"/>
       <c r="M312" s="2"/>
-    </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P312" s="2"/>
+    </row>
+    <row r="313" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H313" s="2"/>
       <c r="I313" s="2"/>
       <c r="M313" s="2"/>
-    </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P313" s="2"/>
+    </row>
+    <row r="314" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H314" s="2"/>
       <c r="I314" s="2"/>
       <c r="M314" s="2"/>
-    </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P314" s="2"/>
+    </row>
+    <row r="315" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H315" s="2"/>
       <c r="I315" s="2"/>
       <c r="M315" s="2"/>
-    </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P315" s="2"/>
+    </row>
+    <row r="316" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H316" s="2"/>
       <c r="I316" s="2"/>
       <c r="M316" s="2"/>
-    </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P316" s="2"/>
+    </row>
+    <row r="317" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H317" s="2"/>
       <c r="I317" s="2"/>
       <c r="M317" s="2"/>
-    </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P317" s="2"/>
+    </row>
+    <row r="318" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H318" s="2"/>
       <c r="I318" s="2"/>
       <c r="M318" s="2"/>
-    </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P318" s="2"/>
+    </row>
+    <row r="319" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H319" s="2"/>
       <c r="I319" s="2"/>
       <c r="M319" s="2"/>
-    </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P319" s="2"/>
+    </row>
+    <row r="320" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H320" s="2"/>
       <c r="I320" s="2"/>
       <c r="M320" s="2"/>
-    </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P320" s="2"/>
+    </row>
+    <row r="321" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H321" s="2"/>
       <c r="I321" s="2"/>
       <c r="M321" s="2"/>
-    </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P321" s="2"/>
+    </row>
+    <row r="322" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H322" s="2"/>
       <c r="I322" s="2"/>
       <c r="M322" s="2"/>
-    </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P322" s="2"/>
+    </row>
+    <row r="323" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H323" s="2"/>
       <c r="I323" s="2"/>
       <c r="M323" s="2"/>
-    </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P323" s="2"/>
+    </row>
+    <row r="324" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H324" s="2"/>
       <c r="I324" s="2"/>
       <c r="M324" s="2"/>
-    </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P324" s="2"/>
+    </row>
+    <row r="325" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="2"/>
       <c r="M325" s="2"/>
-    </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P325" s="2"/>
+    </row>
+    <row r="326" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H326" s="2"/>
       <c r="I326" s="2"/>
       <c r="M326" s="2"/>
-    </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P326" s="2"/>
+    </row>
+    <row r="327" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H327" s="2"/>
       <c r="I327" s="2"/>
       <c r="M327" s="2"/>
-    </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P327" s="2"/>
+    </row>
+    <row r="328" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H328" s="2"/>
       <c r="I328" s="2"/>
       <c r="M328" s="2"/>
-    </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P328" s="2"/>
+    </row>
+    <row r="329" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H329" s="2"/>
       <c r="I329" s="2"/>
       <c r="M329" s="2"/>
-    </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P329" s="2"/>
+    </row>
+    <row r="330" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H330" s="2"/>
       <c r="I330" s="2"/>
       <c r="M330" s="2"/>
-    </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P330" s="2"/>
+    </row>
+    <row r="331" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H331" s="2"/>
       <c r="I331" s="2"/>
       <c r="M331" s="2"/>
-    </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P331" s="2"/>
+    </row>
+    <row r="332" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H332" s="2"/>
       <c r="I332" s="2"/>
       <c r="M332" s="2"/>
-    </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P332" s="2"/>
+    </row>
+    <row r="333" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H333" s="2"/>
       <c r="I333" s="2"/>
       <c r="M333" s="2"/>
-    </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P333" s="2"/>
+    </row>
+    <row r="334" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H334" s="2"/>
       <c r="I334" s="2"/>
       <c r="M334" s="2"/>
-    </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P334" s="2"/>
+    </row>
+    <row r="335" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H335" s="2"/>
       <c r="I335" s="2"/>
       <c r="M335" s="2"/>
-    </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P335" s="2"/>
+    </row>
+    <row r="336" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="2"/>
       <c r="M336" s="2"/>
-    </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P336" s="2"/>
+    </row>
+    <row r="337" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H337" s="2"/>
       <c r="I337" s="2"/>
       <c r="M337" s="2"/>
-    </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P337" s="2"/>
+    </row>
+    <row r="338" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="2"/>
       <c r="M338" s="2"/>
-    </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P338" s="2"/>
+    </row>
+    <row r="339" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H339" s="2"/>
       <c r="I339" s="2"/>
       <c r="M339" s="2"/>
-    </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P339" s="2"/>
+    </row>
+    <row r="340" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H340" s="2"/>
       <c r="I340" s="2"/>
       <c r="M340" s="2"/>
-    </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P340" s="2"/>
+    </row>
+    <row r="341" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H341" s="2"/>
       <c r="I341" s="2"/>
       <c r="M341" s="2"/>
-    </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P341" s="2"/>
+    </row>
+    <row r="342" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H342" s="2"/>
       <c r="I342" s="2"/>
       <c r="M342" s="2"/>
-    </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P342" s="2"/>
+    </row>
+    <row r="343" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H343" s="2"/>
       <c r="I343" s="2"/>
       <c r="M343" s="2"/>
-    </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P343" s="2"/>
+    </row>
+    <row r="344" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H344" s="2"/>
       <c r="I344" s="2"/>
       <c r="M344" s="2"/>
-    </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P344" s="2"/>
+    </row>
+    <row r="345" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H345" s="2"/>
       <c r="I345" s="2"/>
       <c r="M345" s="2"/>
-    </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P345" s="2"/>
+    </row>
+    <row r="346" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H346" s="2"/>
       <c r="I346" s="2"/>
       <c r="M346" s="2"/>
-    </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P346" s="2"/>
+    </row>
+    <row r="347" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H347" s="2"/>
       <c r="I347" s="2"/>
       <c r="M347" s="2"/>
-    </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P347" s="2"/>
+    </row>
+    <row r="348" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H348" s="2"/>
       <c r="I348" s="2"/>
       <c r="M348" s="2"/>
-    </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P348" s="2"/>
+    </row>
+    <row r="349" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H349" s="2"/>
       <c r="I349" s="2"/>
       <c r="M349" s="2"/>
-    </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P349" s="2"/>
+    </row>
+    <row r="350" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H350" s="2"/>
       <c r="I350" s="2"/>
       <c r="M350" s="2"/>
-    </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P350" s="2"/>
+    </row>
+    <row r="351" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H351" s="2"/>
       <c r="I351" s="2"/>
       <c r="M351" s="2"/>
-    </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P351" s="2"/>
+    </row>
+    <row r="352" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H352" s="2"/>
       <c r="I352" s="2"/>
       <c r="M352" s="2"/>
-    </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P352" s="2"/>
+    </row>
+    <row r="353" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H353" s="2"/>
       <c r="I353" s="2"/>
       <c r="M353" s="2"/>
-    </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P353" s="2"/>
+    </row>
+    <row r="354" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="2"/>
       <c r="M354" s="2"/>
-    </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P354" s="2"/>
+    </row>
+    <row r="355" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H355" s="2"/>
       <c r="I355" s="2"/>
       <c r="M355" s="2"/>
-    </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P355" s="2"/>
+    </row>
+    <row r="356" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="2"/>
       <c r="M356" s="2"/>
-    </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P356" s="2"/>
+    </row>
+    <row r="357" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H357" s="2"/>
       <c r="I357" s="2"/>
       <c r="M357" s="2"/>
-    </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P357" s="2"/>
+    </row>
+    <row r="358" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H358" s="2"/>
       <c r="I358" s="2"/>
       <c r="M358" s="2"/>
-    </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P358" s="2"/>
+    </row>
+    <row r="359" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H359" s="2"/>
       <c r="I359" s="2"/>
       <c r="M359" s="2"/>
-    </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P359" s="2"/>
+    </row>
+    <row r="360" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H360" s="2"/>
       <c r="I360" s="2"/>
       <c r="M360" s="2"/>
-    </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P360" s="2"/>
+    </row>
+    <row r="361" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H361" s="2"/>
       <c r="I361" s="2"/>
       <c r="M361" s="2"/>
-    </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P361" s="2"/>
+    </row>
+    <row r="362" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H362" s="2"/>
       <c r="I362" s="2"/>
       <c r="M362" s="2"/>
-    </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P362" s="2"/>
+    </row>
+    <row r="363" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H363" s="2"/>
       <c r="I363" s="2"/>
       <c r="M363" s="2"/>
-    </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P363" s="2"/>
+    </row>
+    <row r="364" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H364" s="2"/>
       <c r="I364" s="2"/>
       <c r="M364" s="2"/>
-    </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P364" s="2"/>
+    </row>
+    <row r="365" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H365" s="2"/>
       <c r="I365" s="2"/>
       <c r="M365" s="2"/>
-    </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P365" s="2"/>
+    </row>
+    <row r="366" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H366" s="2"/>
       <c r="I366" s="2"/>
       <c r="M366" s="2"/>
-    </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P366" s="2"/>
+    </row>
+    <row r="367" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H367" s="2"/>
       <c r="I367" s="2"/>
       <c r="M367" s="2"/>
-    </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P367" s="2"/>
+    </row>
+    <row r="368" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H368" s="2"/>
       <c r="I368" s="2"/>
       <c r="M368" s="2"/>
-    </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P368" s="2"/>
+    </row>
+    <row r="369" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H369" s="2"/>
       <c r="I369" s="2"/>
       <c r="M369" s="2"/>
-    </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P369" s="2"/>
+    </row>
+    <row r="370" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H370" s="2"/>
       <c r="I370" s="2"/>
       <c r="M370" s="2"/>
-    </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P370" s="2"/>
+    </row>
+    <row r="371" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H371" s="2"/>
       <c r="I371" s="2"/>
       <c r="M371" s="2"/>
-    </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P371" s="2"/>
+    </row>
+    <row r="372" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="2"/>
       <c r="M372" s="2"/>
-    </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P372" s="2"/>
+    </row>
+    <row r="373" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H373" s="2"/>
       <c r="I373" s="2"/>
       <c r="M373" s="2"/>
-    </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P373" s="2"/>
+    </row>
+    <row r="374" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H374" s="2"/>
       <c r="I374" s="2"/>
       <c r="M374" s="2"/>
-    </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P374" s="2"/>
+    </row>
+    <row r="375" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H375" s="2"/>
       <c r="I375" s="2"/>
       <c r="M375" s="2"/>
-    </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P375" s="2"/>
+    </row>
+    <row r="376" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H376" s="2"/>
       <c r="I376" s="2"/>
       <c r="M376" s="2"/>
-    </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P376" s="2"/>
+    </row>
+    <row r="377" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H377" s="2"/>
       <c r="I377" s="2"/>
       <c r="M377" s="2"/>
-    </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P377" s="2"/>
+    </row>
+    <row r="378" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H378" s="2"/>
       <c r="I378" s="2"/>
       <c r="M378" s="2"/>
-    </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P378" s="2"/>
+    </row>
+    <row r="379" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H379" s="2"/>
       <c r="I379" s="2"/>
       <c r="M379" s="2"/>
-    </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P379" s="2"/>
+    </row>
+    <row r="380" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H380" s="2"/>
       <c r="I380" s="2"/>
       <c r="M380" s="2"/>
-    </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P380" s="2"/>
+    </row>
+    <row r="381" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H381" s="2"/>
       <c r="I381" s="2"/>
       <c r="M381" s="2"/>
-    </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P381" s="2"/>
+    </row>
+    <row r="382" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="2"/>
       <c r="M382" s="2"/>
-    </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P382" s="2"/>
+    </row>
+    <row r="383" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H383" s="2"/>
       <c r="I383" s="2"/>
       <c r="M383" s="2"/>
-    </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P383" s="2"/>
+    </row>
+    <row r="384" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H384" s="2"/>
       <c r="I384" s="2"/>
       <c r="M384" s="2"/>
-    </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P384" s="2"/>
+    </row>
+    <row r="385" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H385" s="2"/>
       <c r="I385" s="2"/>
       <c r="M385" s="2"/>
-    </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P385" s="2"/>
+    </row>
+    <row r="386" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H386" s="2"/>
       <c r="I386" s="2"/>
       <c r="M386" s="2"/>
-    </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P386" s="2"/>
+    </row>
+    <row r="387" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H387" s="2"/>
       <c r="I387" s="2"/>
       <c r="M387" s="2"/>
-    </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P387" s="2"/>
+    </row>
+    <row r="388" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H388" s="2"/>
       <c r="I388" s="2"/>
       <c r="M388" s="2"/>
-    </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P388" s="2"/>
+    </row>
+    <row r="389" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H389" s="2"/>
       <c r="I389" s="2"/>
       <c r="M389" s="2"/>
-    </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P389" s="2"/>
+    </row>
+    <row r="390" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H390" s="2"/>
       <c r="I390" s="2"/>
       <c r="M390" s="2"/>
-    </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P390" s="2"/>
+    </row>
+    <row r="391" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H391" s="2"/>
       <c r="I391" s="2"/>
       <c r="M391" s="2"/>
-    </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P391" s="2"/>
+    </row>
+    <row r="392" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H392" s="2"/>
       <c r="I392" s="2"/>
       <c r="M392" s="2"/>
-    </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P392" s="2"/>
+    </row>
+    <row r="393" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H393" s="2"/>
       <c r="I393" s="2"/>
       <c r="M393" s="2"/>
-    </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P393" s="2"/>
+    </row>
+    <row r="394" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H394" s="2"/>
       <c r="I394" s="2"/>
       <c r="M394" s="2"/>
-    </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P394" s="2"/>
+    </row>
+    <row r="395" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H395" s="2"/>
       <c r="I395" s="2"/>
       <c r="M395" s="2"/>
-    </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P395" s="2"/>
+    </row>
+    <row r="396" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H396" s="2"/>
       <c r="I396" s="2"/>
       <c r="M396" s="2"/>
-    </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P396" s="2"/>
+    </row>
+    <row r="397" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H397" s="2"/>
       <c r="I397" s="2"/>
       <c r="M397" s="2"/>
-    </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P397" s="2"/>
+    </row>
+    <row r="398" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H398" s="2"/>
       <c r="I398" s="2"/>
       <c r="M398" s="2"/>
-    </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P398" s="2"/>
+    </row>
+    <row r="399" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H399" s="2"/>
       <c r="I399" s="2"/>
       <c r="M399" s="2"/>
-    </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P399" s="2"/>
+    </row>
+    <row r="400" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H400" s="2"/>
       <c r="I400" s="2"/>
       <c r="M400" s="2"/>
-    </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P400" s="2"/>
+    </row>
+    <row r="401" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H401" s="2"/>
       <c r="I401" s="2"/>
       <c r="M401" s="2"/>
-    </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P401" s="2"/>
+    </row>
+    <row r="402" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H402" s="2"/>
       <c r="I402" s="2"/>
       <c r="M402" s="2"/>
-    </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P402" s="2"/>
+    </row>
+    <row r="403" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H403" s="2"/>
       <c r="I403" s="2"/>
       <c r="M403" s="2"/>
-    </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P403" s="2"/>
+    </row>
+    <row r="404" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H404" s="2"/>
       <c r="I404" s="2"/>
       <c r="M404" s="2"/>
-    </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P404" s="2"/>
+    </row>
+    <row r="405" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H405" s="2"/>
       <c r="I405" s="2"/>
       <c r="M405" s="2"/>
-    </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P405" s="2"/>
+    </row>
+    <row r="406" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H406" s="2"/>
       <c r="I406" s="2"/>
       <c r="M406" s="2"/>
-    </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P406" s="2"/>
+    </row>
+    <row r="407" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H407" s="2"/>
       <c r="I407" s="2"/>
       <c r="M407" s="2"/>
-    </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P407" s="2"/>
+    </row>
+    <row r="408" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H408" s="2"/>
       <c r="I408" s="2"/>
       <c r="M408" s="2"/>
-    </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P408" s="2"/>
+    </row>
+    <row r="409" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H409" s="2"/>
       <c r="I409" s="2"/>
       <c r="M409" s="2"/>
-    </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P409" s="2"/>
+    </row>
+    <row r="410" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H410" s="2"/>
       <c r="I410" s="2"/>
       <c r="M410" s="2"/>
-    </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P410" s="2"/>
+    </row>
+    <row r="411" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H411" s="2"/>
       <c r="I411" s="2"/>
       <c r="M411" s="2"/>
-    </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P411" s="2"/>
+    </row>
+    <row r="412" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H412" s="2"/>
       <c r="I412" s="2"/>
       <c r="M412" s="2"/>
-    </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P412" s="2"/>
+    </row>
+    <row r="413" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H413" s="2"/>
       <c r="I413" s="2"/>
       <c r="M413" s="2"/>
-    </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P413" s="2"/>
+    </row>
+    <row r="414" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H414" s="2"/>
       <c r="I414" s="2"/>
       <c r="M414" s="2"/>
-    </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P414" s="2"/>
+    </row>
+    <row r="415" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H415" s="2"/>
       <c r="I415" s="2"/>
       <c r="M415" s="2"/>
-    </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P415" s="2"/>
+    </row>
+    <row r="416" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H416" s="2"/>
       <c r="I416" s="2"/>
       <c r="M416" s="2"/>
-    </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P416" s="2"/>
+    </row>
+    <row r="417" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H417" s="2"/>
       <c r="I417" s="2"/>
       <c r="M417" s="2"/>
-    </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P417" s="2"/>
+    </row>
+    <row r="418" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H418" s="2"/>
       <c r="I418" s="2"/>
       <c r="M418" s="2"/>
-    </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P418" s="2"/>
+    </row>
+    <row r="419" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H419" s="2"/>
       <c r="I419" s="2"/>
       <c r="M419" s="2"/>
-    </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P419" s="2"/>
+    </row>
+    <row r="420" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H420" s="2"/>
       <c r="I420" s="2"/>
       <c r="M420" s="2"/>
-    </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P420" s="2"/>
+    </row>
+    <row r="421" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H421" s="2"/>
       <c r="I421" s="2"/>
       <c r="M421" s="2"/>
-    </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P421" s="2"/>
+    </row>
+    <row r="422" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H422" s="2"/>
       <c r="I422" s="2"/>
       <c r="M422" s="2"/>
-    </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P422" s="2"/>
+    </row>
+    <row r="423" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H423" s="2"/>
       <c r="I423" s="2"/>
       <c r="M423" s="2"/>
-    </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P423" s="2"/>
+    </row>
+    <row r="424" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H424" s="2"/>
       <c r="I424" s="2"/>
       <c r="M424" s="2"/>
-    </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P424" s="2"/>
+    </row>
+    <row r="425" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H425" s="2"/>
       <c r="I425" s="2"/>
       <c r="M425" s="2"/>
-    </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P425" s="2"/>
+    </row>
+    <row r="426" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H426" s="2"/>
       <c r="I426" s="2"/>
       <c r="M426" s="2"/>
-    </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P426" s="2"/>
+    </row>
+    <row r="427" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H427" s="2"/>
       <c r="I427" s="2"/>
       <c r="M427" s="2"/>
-    </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P427" s="2"/>
+    </row>
+    <row r="428" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H428" s="2"/>
       <c r="I428" s="2"/>
       <c r="M428" s="2"/>
-    </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P428" s="2"/>
+    </row>
+    <row r="429" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H429" s="2"/>
       <c r="I429" s="2"/>
       <c r="M429" s="2"/>
-    </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P429" s="2"/>
+    </row>
+    <row r="430" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H430" s="2"/>
       <c r="I430" s="2"/>
       <c r="M430" s="2"/>
-    </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P430" s="2"/>
+    </row>
+    <row r="431" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H431" s="2"/>
       <c r="I431" s="2"/>
       <c r="M431" s="2"/>
-    </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P431" s="2"/>
+    </row>
+    <row r="432" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H432" s="2"/>
       <c r="I432" s="2"/>
       <c r="M432" s="2"/>
-    </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P432" s="2"/>
+    </row>
+    <row r="433" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H433" s="2"/>
       <c r="I433" s="2"/>
       <c r="M433" s="2"/>
-    </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P433" s="2"/>
+    </row>
+    <row r="434" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H434" s="2"/>
       <c r="I434" s="2"/>
       <c r="M434" s="2"/>
-    </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P434" s="2"/>
+    </row>
+    <row r="435" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H435" s="2"/>
       <c r="I435" s="2"/>
       <c r="M435" s="2"/>
-    </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P435" s="2"/>
+    </row>
+    <row r="436" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H436" s="2"/>
       <c r="I436" s="2"/>
       <c r="M436" s="2"/>
-    </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P436" s="2"/>
+    </row>
+    <row r="437" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H437" s="2"/>
       <c r="I437" s="2"/>
       <c r="M437" s="2"/>
-    </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P437" s="2"/>
+    </row>
+    <row r="438" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H438" s="2"/>
       <c r="I438" s="2"/>
       <c r="M438" s="2"/>
-    </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P438" s="2"/>
+    </row>
+    <row r="439" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H439" s="2"/>
       <c r="I439" s="2"/>
       <c r="M439" s="2"/>
-    </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P439" s="2"/>
+    </row>
+    <row r="440" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H440" s="2"/>
       <c r="I440" s="2"/>
       <c r="M440" s="2"/>
-    </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P440" s="2"/>
+    </row>
+    <row r="441" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H441" s="2"/>
       <c r="I441" s="2"/>
       <c r="M441" s="2"/>
-    </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P441" s="2"/>
+    </row>
+    <row r="442" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H442" s="2"/>
       <c r="I442" s="2"/>
       <c r="M442" s="2"/>
-    </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P442" s="2"/>
+    </row>
+    <row r="443" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H443" s="2"/>
       <c r="I443" s="2"/>
       <c r="M443" s="2"/>
-    </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P443" s="2"/>
+    </row>
+    <row r="444" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H444" s="2"/>
       <c r="I444" s="2"/>
       <c r="M444" s="2"/>
-    </row>
-    <row r="445" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P444" s="2"/>
+    </row>
+    <row r="445" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H445" s="2"/>
       <c r="I445" s="2"/>
       <c r="M445" s="2"/>
-    </row>
-    <row r="446" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P445" s="2"/>
+    </row>
+    <row r="446" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H446" s="2"/>
       <c r="I446" s="2"/>
       <c r="M446" s="2"/>
-    </row>
-    <row r="447" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P446" s="2"/>
+    </row>
+    <row r="447" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H447" s="2"/>
       <c r="I447" s="2"/>
       <c r="M447" s="2"/>
-    </row>
-    <row r="448" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P447" s="2"/>
+    </row>
+    <row r="448" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H448" s="2"/>
       <c r="I448" s="2"/>
       <c r="M448" s="2"/>
-    </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P448" s="2"/>
+    </row>
+    <row r="449" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H449" s="2"/>
       <c r="I449" s="2"/>
       <c r="M449" s="2"/>
-    </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P449" s="2"/>
+    </row>
+    <row r="450" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H450" s="2"/>
       <c r="I450" s="2"/>
       <c r="M450" s="2"/>
-    </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P450" s="2"/>
+    </row>
+    <row r="451" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H451" s="2"/>
       <c r="I451" s="2"/>
       <c r="M451" s="2"/>
-    </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P451" s="2"/>
+    </row>
+    <row r="452" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H452" s="2"/>
       <c r="I452" s="2"/>
       <c r="M452" s="2"/>
-    </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P452" s="2"/>
+    </row>
+    <row r="453" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H453" s="2"/>
       <c r="I453" s="2"/>
       <c r="M453" s="2"/>
-    </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P453" s="2"/>
+    </row>
+    <row r="454" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H454" s="2"/>
       <c r="I454" s="2"/>
       <c r="M454" s="2"/>
-    </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P454" s="2"/>
+    </row>
+    <row r="455" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H455" s="2"/>
       <c r="I455" s="2"/>
       <c r="M455" s="2"/>
-    </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P455" s="2"/>
+    </row>
+    <row r="456" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H456" s="2"/>
       <c r="I456" s="2"/>
       <c r="M456" s="2"/>
-    </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P456" s="2"/>
+    </row>
+    <row r="457" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H457" s="2"/>
       <c r="I457" s="2"/>
       <c r="M457" s="2"/>
-    </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P457" s="2"/>
+    </row>
+    <row r="458" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H458" s="2"/>
       <c r="I458" s="2"/>
       <c r="M458" s="2"/>
-    </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P458" s="2"/>
+    </row>
+    <row r="459" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H459" s="2"/>
       <c r="I459" s="2"/>
       <c r="M459" s="2"/>
-    </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P459" s="2"/>
+    </row>
+    <row r="460" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H460" s="2"/>
       <c r="I460" s="2"/>
       <c r="M460" s="2"/>
-    </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P460" s="2"/>
+    </row>
+    <row r="461" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H461" s="2"/>
       <c r="I461" s="2"/>
       <c r="M461" s="2"/>
-    </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P461" s="2"/>
+    </row>
+    <row r="462" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H462" s="2"/>
       <c r="I462" s="2"/>
       <c r="M462" s="2"/>
-    </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P462" s="2"/>
+    </row>
+    <row r="463" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H463" s="2"/>
       <c r="I463" s="2"/>
       <c r="M463" s="2"/>
-    </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P463" s="2"/>
+    </row>
+    <row r="464" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H464" s="2"/>
       <c r="I464" s="2"/>
       <c r="M464" s="2"/>
-    </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P464" s="2"/>
+    </row>
+    <row r="465" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H465" s="2"/>
       <c r="I465" s="2"/>
       <c r="M465" s="2"/>
-    </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P465" s="2"/>
+    </row>
+    <row r="466" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H466" s="2"/>
       <c r="I466" s="2"/>
       <c r="M466" s="2"/>
-    </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P466" s="2"/>
+    </row>
+    <row r="467" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H467" s="2"/>
       <c r="I467" s="2"/>
       <c r="M467" s="2"/>
-    </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P467" s="2"/>
+    </row>
+    <row r="468" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H468" s="2"/>
       <c r="I468" s="2"/>
       <c r="M468" s="2"/>
-    </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P468" s="2"/>
+    </row>
+    <row r="469" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H469" s="2"/>
       <c r="I469" s="2"/>
       <c r="M469" s="2"/>
-    </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P469" s="2"/>
+    </row>
+    <row r="470" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H470" s="2"/>
       <c r="I470" s="2"/>
       <c r="M470" s="2"/>
-    </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P470" s="2"/>
+    </row>
+    <row r="471" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H471" s="2"/>
       <c r="I471" s="2"/>
       <c r="M471" s="2"/>
-    </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P471" s="2"/>
+    </row>
+    <row r="472" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H472" s="2"/>
       <c r="I472" s="2"/>
       <c r="M472" s="2"/>
-    </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P472" s="2"/>
+    </row>
+    <row r="473" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H473" s="2"/>
       <c r="I473" s="2"/>
       <c r="M473" s="2"/>
-    </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P473" s="2"/>
+    </row>
+    <row r="474" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H474" s="2"/>
       <c r="I474" s="2"/>
       <c r="M474" s="2"/>
-    </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P474" s="2"/>
+    </row>
+    <row r="475" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H475" s="2"/>
       <c r="I475" s="2"/>
       <c r="M475" s="2"/>
-    </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P475" s="2"/>
+    </row>
+    <row r="476" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H476" s="2"/>
       <c r="I476" s="2"/>
       <c r="M476" s="2"/>
-    </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P476" s="2"/>
+    </row>
+    <row r="477" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H477" s="2"/>
       <c r="I477" s="2"/>
       <c r="M477" s="2"/>
-    </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P477" s="2"/>
+    </row>
+    <row r="478" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H478" s="2"/>
       <c r="I478" s="2"/>
       <c r="M478" s="2"/>
-    </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P478" s="2"/>
+    </row>
+    <row r="479" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H479" s="2"/>
       <c r="I479" s="2"/>
       <c r="M479" s="2"/>
-    </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P479" s="2"/>
+    </row>
+    <row r="480" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H480" s="2"/>
       <c r="I480" s="2"/>
       <c r="M480" s="2"/>
-    </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P480" s="2"/>
+    </row>
+    <row r="481" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H481" s="2"/>
       <c r="I481" s="2"/>
       <c r="M481" s="2"/>
-    </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P481" s="2"/>
+    </row>
+    <row r="482" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H482" s="2"/>
       <c r="I482" s="2"/>
       <c r="M482" s="2"/>
-    </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P482" s="2"/>
+    </row>
+    <row r="483" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H483" s="2"/>
       <c r="I483" s="2"/>
       <c r="M483" s="2"/>
-    </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P483" s="2"/>
+    </row>
+    <row r="484" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H484" s="2"/>
       <c r="I484" s="2"/>
       <c r="M484" s="2"/>
-    </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P484" s="2"/>
+    </row>
+    <row r="485" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H485" s="2"/>
       <c r="I485" s="2"/>
       <c r="M485" s="2"/>
-    </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P485" s="2"/>
+    </row>
+    <row r="486" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H486" s="2"/>
       <c r="I486" s="2"/>
       <c r="M486" s="2"/>
-    </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P486" s="2"/>
+    </row>
+    <row r="487" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H487" s="2"/>
       <c r="I487" s="2"/>
       <c r="M487" s="2"/>
-    </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P487" s="2"/>
+    </row>
+    <row r="488" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H488" s="2"/>
       <c r="I488" s="2"/>
       <c r="M488" s="2"/>
-    </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P488" s="2"/>
+    </row>
+    <row r="489" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H489" s="2"/>
       <c r="I489" s="2"/>
       <c r="M489" s="2"/>
-    </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P489" s="2"/>
+    </row>
+    <row r="490" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H490" s="2"/>
       <c r="I490" s="2"/>
       <c r="M490" s="2"/>
-    </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P490" s="2"/>
+    </row>
+    <row r="491" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H491" s="2"/>
       <c r="I491" s="2"/>
       <c r="M491" s="2"/>
-    </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P491" s="2"/>
+    </row>
+    <row r="492" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H492" s="2"/>
       <c r="I492" s="2"/>
       <c r="M492" s="2"/>
-    </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P492" s="2"/>
+    </row>
+    <row r="493" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H493" s="2"/>
       <c r="I493" s="2"/>
       <c r="M493" s="2"/>
-    </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P493" s="2"/>
+    </row>
+    <row r="494" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H494" s="2"/>
       <c r="I494" s="2"/>
       <c r="M494" s="2"/>
-    </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P494" s="2"/>
+    </row>
+    <row r="495" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H495" s="2"/>
       <c r="I495" s="2"/>
       <c r="M495" s="2"/>
-    </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P495" s="2"/>
+    </row>
+    <row r="496" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H496" s="2"/>
       <c r="I496" s="2"/>
       <c r="M496" s="2"/>
-    </row>
-    <row r="497" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P496" s="2"/>
+    </row>
+    <row r="497" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H497" s="2"/>
       <c r="I497" s="2"/>
       <c r="M497" s="2"/>
-    </row>
-    <row r="498" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P497" s="2"/>
+    </row>
+    <row r="498" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H498" s="2"/>
       <c r="I498" s="2"/>
       <c r="M498" s="2"/>
-    </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P498" s="2"/>
+    </row>
+    <row r="499" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H499" s="2"/>
       <c r="I499" s="2"/>
       <c r="M499" s="2"/>
-    </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P499" s="2"/>
+    </row>
+    <row r="500" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H500" s="2"/>
       <c r="I500" s="2"/>
       <c r="M500" s="2"/>
-    </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P500" s="2"/>
+    </row>
+    <row r="501" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H501" s="2"/>
       <c r="I501" s="2"/>
       <c r="M501" s="2"/>
-    </row>
-    <row r="502" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P501" s="2"/>
+    </row>
+    <row r="502" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H502" s="2"/>
       <c r="I502" s="2"/>
       <c r="M502" s="2"/>
-    </row>
-    <row r="503" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P502" s="2"/>
+    </row>
+    <row r="503" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H503" s="2"/>
       <c r="I503" s="2"/>
       <c r="M503" s="2"/>
-    </row>
-    <row r="504" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P503" s="2"/>
+    </row>
+    <row r="504" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H504" s="2"/>
       <c r="I504" s="2"/>
       <c r="M504" s="2"/>
-    </row>
-    <row r="505" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P504" s="2"/>
+    </row>
+    <row r="505" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H505" s="2"/>
       <c r="I505" s="2"/>
       <c r="M505" s="2"/>
-    </row>
-    <row r="506" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P505" s="2"/>
+    </row>
+    <row r="506" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H506" s="2"/>
       <c r="I506" s="2"/>
       <c r="M506" s="2"/>
-    </row>
-    <row r="507" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P506" s="2"/>
+    </row>
+    <row r="507" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H507" s="2"/>
       <c r="I507" s="2"/>
       <c r="M507" s="2"/>
-    </row>
-    <row r="508" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P507" s="2"/>
+    </row>
+    <row r="508" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H508" s="2"/>
       <c r="I508" s="2"/>
       <c r="M508" s="2"/>
-    </row>
-    <row r="509" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P508" s="2"/>
+    </row>
+    <row r="509" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H509" s="2"/>
       <c r="I509" s="2"/>
       <c r="M509" s="2"/>
-    </row>
-    <row r="510" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P509" s="2"/>
+    </row>
+    <row r="510" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H510" s="2"/>
       <c r="I510" s="2"/>
       <c r="M510" s="2"/>
-    </row>
-    <row r="511" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P510" s="2"/>
+    </row>
+    <row r="511" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H511" s="2"/>
       <c r="I511" s="2"/>
       <c r="M511" s="2"/>
-    </row>
-    <row r="512" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P511" s="2"/>
+    </row>
+    <row r="512" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H512" s="2"/>
       <c r="I512" s="2"/>
       <c r="M512" s="2"/>
-    </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P512" s="2"/>
+    </row>
+    <row r="513" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H513" s="2"/>
       <c r="I513" s="2"/>
       <c r="M513" s="2"/>
-    </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P513" s="2"/>
+    </row>
+    <row r="514" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H514" s="2"/>
       <c r="I514" s="2"/>
       <c r="M514" s="2"/>
-    </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P514" s="2"/>
+    </row>
+    <row r="515" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H515" s="2"/>
       <c r="I515" s="2"/>
       <c r="M515" s="2"/>
-    </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P515" s="2"/>
+    </row>
+    <row r="516" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H516" s="2"/>
       <c r="I516" s="2"/>
       <c r="M516" s="2"/>
-    </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P516" s="2"/>
+    </row>
+    <row r="517" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H517" s="2"/>
       <c r="I517" s="2"/>
       <c r="M517" s="2"/>
-    </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P517" s="2"/>
+    </row>
+    <row r="518" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H518" s="2"/>
       <c r="I518" s="2"/>
       <c r="M518" s="2"/>
-    </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P518" s="2"/>
+    </row>
+    <row r="519" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H519" s="2"/>
       <c r="I519" s="2"/>
       <c r="M519" s="2"/>
-    </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P519" s="2"/>
+    </row>
+    <row r="520" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H520" s="2"/>
       <c r="I520" s="2"/>
       <c r="M520" s="2"/>
-    </row>
-    <row r="521" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P520" s="2"/>
+    </row>
+    <row r="521" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H521" s="2"/>
       <c r="I521" s="2"/>
       <c r="M521" s="2"/>
-    </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P521" s="2"/>
+    </row>
+    <row r="522" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H522" s="2"/>
       <c r="I522" s="2"/>
       <c r="M522" s="2"/>
-    </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P522" s="2"/>
+    </row>
+    <row r="523" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H523" s="2"/>
       <c r="I523" s="2"/>
       <c r="M523" s="2"/>
-    </row>
-    <row r="524" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P523" s="2"/>
+    </row>
+    <row r="524" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H524" s="2"/>
       <c r="I524" s="2"/>
       <c r="M524" s="2"/>
-    </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P524" s="2"/>
+    </row>
+    <row r="525" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H525" s="2"/>
       <c r="I525" s="2"/>
       <c r="M525" s="2"/>
-    </row>
-    <row r="526" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P525" s="2"/>
+    </row>
+    <row r="526" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H526" s="2"/>
       <c r="I526" s="2"/>
       <c r="M526" s="2"/>
-    </row>
-    <row r="527" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P526" s="2"/>
+    </row>
+    <row r="527" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H527" s="2"/>
       <c r="I527" s="2"/>
       <c r="M527" s="2"/>
-    </row>
-    <row r="528" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P527" s="2"/>
+    </row>
+    <row r="528" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H528" s="2"/>
       <c r="I528" s="2"/>
       <c r="M528" s="2"/>
-    </row>
-    <row r="529" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P528" s="2"/>
+    </row>
+    <row r="529" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H529" s="2"/>
       <c r="I529" s="2"/>
       <c r="M529" s="2"/>
-    </row>
-    <row r="530" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P529" s="2"/>
+    </row>
+    <row r="530" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H530" s="2"/>
       <c r="I530" s="2"/>
       <c r="M530" s="2"/>
-    </row>
-    <row r="531" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P530" s="2"/>
+    </row>
+    <row r="531" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H531" s="2"/>
       <c r="I531" s="2"/>
       <c r="M531" s="2"/>
-    </row>
-    <row r="532" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P531" s="2"/>
+    </row>
+    <row r="532" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H532" s="2"/>
       <c r="I532" s="2"/>
       <c r="M532" s="2"/>
-    </row>
-    <row r="533" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P532" s="2"/>
+    </row>
+    <row r="533" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H533" s="2"/>
       <c r="I533" s="2"/>
       <c r="M533" s="2"/>
-    </row>
-    <row r="534" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P533" s="2"/>
+    </row>
+    <row r="534" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H534" s="2"/>
       <c r="I534" s="2"/>
       <c r="M534" s="2"/>
-    </row>
-    <row r="535" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P534" s="2"/>
+    </row>
+    <row r="535" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H535" s="2"/>
       <c r="I535" s="2"/>
       <c r="M535" s="2"/>
-    </row>
-    <row r="536" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P535" s="2"/>
+    </row>
+    <row r="536" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H536" s="2"/>
       <c r="I536" s="2"/>
       <c r="M536" s="2"/>
-    </row>
-    <row r="537" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P536" s="2"/>
+    </row>
+    <row r="537" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H537" s="2"/>
       <c r="I537" s="2"/>
       <c r="M537" s="2"/>
-    </row>
-    <row r="538" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P537" s="2"/>
+    </row>
+    <row r="538" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H538" s="2"/>
       <c r="I538" s="2"/>
       <c r="M538" s="2"/>
-    </row>
-    <row r="539" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P538" s="2"/>
+    </row>
+    <row r="539" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H539" s="2"/>
       <c r="I539" s="2"/>
       <c r="M539" s="2"/>
-    </row>
-    <row r="540" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P539" s="2"/>
+    </row>
+    <row r="540" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H540" s="2"/>
       <c r="I540" s="2"/>
       <c r="M540" s="2"/>
-    </row>
-    <row r="541" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P540" s="2"/>
+    </row>
+    <row r="541" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H541" s="2"/>
       <c r="I541" s="2"/>
       <c r="M541" s="2"/>
-    </row>
-    <row r="542" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P541" s="2"/>
+    </row>
+    <row r="542" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H542" s="2"/>
       <c r="I542" s="2"/>
       <c r="M542" s="2"/>
-    </row>
-    <row r="543" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P542" s="2"/>
+    </row>
+    <row r="543" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H543" s="2"/>
       <c r="I543" s="2"/>
       <c r="M543" s="2"/>
-    </row>
-    <row r="544" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P543" s="2"/>
+    </row>
+    <row r="544" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H544" s="2"/>
       <c r="I544" s="2"/>
       <c r="M544" s="2"/>
-    </row>
-    <row r="545" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P544" s="2"/>
+    </row>
+    <row r="545" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H545" s="2"/>
       <c r="I545" s="2"/>
       <c r="M545" s="2"/>
-    </row>
-    <row r="546" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P545" s="2"/>
+    </row>
+    <row r="546" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H546" s="2"/>
       <c r="I546" s="2"/>
       <c r="M546" s="2"/>
-    </row>
-    <row r="547" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P546" s="2"/>
+    </row>
+    <row r="547" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H547" s="2"/>
       <c r="I547" s="2"/>
       <c r="M547" s="2"/>
-    </row>
-    <row r="548" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P547" s="2"/>
+    </row>
+    <row r="548" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H548" s="2"/>
       <c r="I548" s="2"/>
       <c r="M548" s="2"/>
-    </row>
-    <row r="549" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P548" s="2"/>
+    </row>
+    <row r="549" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H549" s="2"/>
       <c r="I549" s="2"/>
       <c r="M549" s="2"/>
-    </row>
-    <row r="550" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P549" s="2"/>
+    </row>
+    <row r="550" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H550" s="2"/>
       <c r="I550" s="2"/>
       <c r="M550" s="2"/>
-    </row>
-    <row r="551" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P550" s="2"/>
+    </row>
+    <row r="551" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H551" s="2"/>
       <c r="I551" s="2"/>
       <c r="M551" s="2"/>
-    </row>
-    <row r="552" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P551" s="2"/>
+    </row>
+    <row r="552" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H552" s="2"/>
       <c r="I552" s="2"/>
       <c r="M552" s="2"/>
-    </row>
-    <row r="553" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P552" s="2"/>
+    </row>
+    <row r="553" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H553" s="2"/>
       <c r="I553" s="2"/>
       <c r="M553" s="2"/>
-    </row>
-    <row r="554" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P553" s="2"/>
+    </row>
+    <row r="554" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H554" s="2"/>
       <c r="I554" s="2"/>
       <c r="M554" s="2"/>
-    </row>
-    <row r="555" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P554" s="2"/>
+    </row>
+    <row r="555" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H555" s="2"/>
       <c r="I555" s="2"/>
       <c r="M555" s="2"/>
-    </row>
-    <row r="556" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P555" s="2"/>
+    </row>
+    <row r="556" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H556" s="2"/>
       <c r="I556" s="2"/>
       <c r="M556" s="2"/>
-    </row>
-    <row r="557" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P556" s="2"/>
+    </row>
+    <row r="557" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H557" s="2"/>
       <c r="I557" s="2"/>
       <c r="M557" s="2"/>
-    </row>
-    <row r="558" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P557" s="2"/>
+    </row>
+    <row r="558" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H558" s="2"/>
       <c r="I558" s="2"/>
       <c r="M558" s="2"/>
-    </row>
-    <row r="559" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P558" s="2"/>
+    </row>
+    <row r="559" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H559" s="2"/>
       <c r="I559" s="2"/>
       <c r="M559" s="2"/>
-    </row>
-    <row r="560" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P559" s="2"/>
+    </row>
+    <row r="560" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H560" s="2"/>
       <c r="I560" s="2"/>
       <c r="M560" s="2"/>
-    </row>
-    <row r="561" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P560" s="2"/>
+    </row>
+    <row r="561" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H561" s="2"/>
       <c r="I561" s="2"/>
       <c r="M561" s="2"/>
-    </row>
-    <row r="562" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P561" s="2"/>
+    </row>
+    <row r="562" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H562" s="2"/>
       <c r="I562" s="2"/>
       <c r="M562" s="2"/>
-    </row>
-    <row r="563" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P562" s="2"/>
+    </row>
+    <row r="563" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H563" s="2"/>
       <c r="I563" s="2"/>
       <c r="M563" s="2"/>
-    </row>
-    <row r="564" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P563" s="2"/>
+    </row>
+    <row r="564" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H564" s="2"/>
       <c r="I564" s="2"/>
       <c r="M564" s="2"/>
-    </row>
-    <row r="565" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P564" s="2"/>
+    </row>
+    <row r="565" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H565" s="2"/>
       <c r="I565" s="2"/>
       <c r="M565" s="2"/>
-    </row>
-    <row r="566" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P565" s="2"/>
+    </row>
+    <row r="566" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H566" s="2"/>
       <c r="I566" s="2"/>
       <c r="M566" s="2"/>
-    </row>
-    <row r="567" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P566" s="2"/>
+    </row>
+    <row r="567" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H567" s="2"/>
       <c r="I567" s="2"/>
       <c r="M567" s="2"/>
-    </row>
-    <row r="568" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P567" s="2"/>
+    </row>
+    <row r="568" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H568" s="2"/>
       <c r="I568" s="2"/>
       <c r="M568" s="2"/>
-    </row>
-    <row r="569" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P568" s="2"/>
+    </row>
+    <row r="569" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H569" s="2"/>
       <c r="I569" s="2"/>
       <c r="M569" s="2"/>
-    </row>
-    <row r="570" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P569" s="2"/>
+    </row>
+    <row r="570" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H570" s="2"/>
       <c r="I570" s="2"/>
       <c r="M570" s="2"/>
-    </row>
-    <row r="571" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P570" s="2"/>
+    </row>
+    <row r="571" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H571" s="2"/>
       <c r="I571" s="2"/>
       <c r="M571" s="2"/>
-    </row>
-    <row r="572" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P571" s="2"/>
+    </row>
+    <row r="572" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H572" s="2"/>
       <c r="I572" s="2"/>
       <c r="M572" s="2"/>
-    </row>
-    <row r="573" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P572" s="2"/>
+    </row>
+    <row r="573" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H573" s="2"/>
       <c r="I573" s="2"/>
       <c r="M573" s="2"/>
-    </row>
-    <row r="574" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P573" s="2"/>
+    </row>
+    <row r="574" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H574" s="2"/>
       <c r="I574" s="2"/>
       <c r="M574" s="2"/>
-    </row>
-    <row r="575" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P574" s="2"/>
+    </row>
+    <row r="575" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H575" s="2"/>
       <c r="I575" s="2"/>
       <c r="M575" s="2"/>
-    </row>
-    <row r="576" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P575" s="2"/>
+    </row>
+    <row r="576" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H576" s="2"/>
       <c r="I576" s="2"/>
       <c r="M576" s="2"/>
-    </row>
-    <row r="577" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P576" s="2"/>
+    </row>
+    <row r="577" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H577" s="2"/>
       <c r="I577" s="2"/>
       <c r="M577" s="2"/>
-    </row>
-    <row r="578" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P577" s="2"/>
+    </row>
+    <row r="578" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H578" s="2"/>
       <c r="I578" s="2"/>
       <c r="M578" s="2"/>
-    </row>
-    <row r="579" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P578" s="2"/>
+    </row>
+    <row r="579" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H579" s="2"/>
       <c r="I579" s="2"/>
       <c r="M579" s="2"/>
-    </row>
-    <row r="580" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P579" s="2"/>
+    </row>
+    <row r="580" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H580" s="2"/>
       <c r="I580" s="2"/>
       <c r="M580" s="2"/>
-    </row>
-    <row r="581" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P580" s="2"/>
+    </row>
+    <row r="581" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H581" s="2"/>
       <c r="I581" s="2"/>
       <c r="M581" s="2"/>
-    </row>
-    <row r="582" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P581" s="2"/>
+    </row>
+    <row r="582" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H582" s="2"/>
       <c r="I582" s="2"/>
       <c r="M582" s="2"/>
-    </row>
-    <row r="583" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P582" s="2"/>
+    </row>
+    <row r="583" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H583" s="2"/>
       <c r="I583" s="2"/>
       <c r="M583" s="2"/>
-    </row>
-    <row r="584" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P583" s="2"/>
+    </row>
+    <row r="584" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H584" s="2"/>
       <c r="I584" s="2"/>
       <c r="M584" s="2"/>
-    </row>
-    <row r="585" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P584" s="2"/>
+    </row>
+    <row r="585" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H585" s="2"/>
       <c r="I585" s="2"/>
       <c r="M585" s="2"/>
-    </row>
-    <row r="586" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P585" s="2"/>
+    </row>
+    <row r="586" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H586" s="2"/>
       <c r="I586" s="2"/>
       <c r="M586" s="2"/>
-    </row>
-    <row r="587" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P586" s="2"/>
+    </row>
+    <row r="587" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H587" s="2"/>
       <c r="I587" s="2"/>
       <c r="M587" s="2"/>
-    </row>
-    <row r="588" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P587" s="2"/>
+    </row>
+    <row r="588" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H588" s="2"/>
       <c r="I588" s="2"/>
       <c r="M588" s="2"/>
-    </row>
-    <row r="589" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P588" s="2"/>
+    </row>
+    <row r="589" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H589" s="2"/>
       <c r="I589" s="2"/>
       <c r="M589" s="2"/>
-    </row>
-    <row r="590" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P589" s="2"/>
+    </row>
+    <row r="590" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H590" s="2"/>
       <c r="I590" s="2"/>
       <c r="M590" s="2"/>
-    </row>
-    <row r="591" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P590" s="2"/>
+    </row>
+    <row r="591" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H591" s="2"/>
       <c r="I591" s="2"/>
       <c r="M591" s="2"/>
-    </row>
-    <row r="592" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P591" s="2"/>
+    </row>
+    <row r="592" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H592" s="2"/>
       <c r="I592" s="2"/>
       <c r="M592" s="2"/>
-    </row>
-    <row r="593" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P592" s="2"/>
+    </row>
+    <row r="593" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H593" s="2"/>
       <c r="I593" s="2"/>
       <c r="M593" s="2"/>
-    </row>
-    <row r="594" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P593" s="2"/>
+    </row>
+    <row r="594" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H594" s="2"/>
       <c r="I594" s="2"/>
       <c r="M594" s="2"/>
-    </row>
-    <row r="595" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P594" s="2"/>
+    </row>
+    <row r="595" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H595" s="2"/>
       <c r="I595" s="2"/>
       <c r="M595" s="2"/>
-    </row>
-    <row r="596" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P595" s="2"/>
+    </row>
+    <row r="596" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H596" s="2"/>
       <c r="I596" s="2"/>
       <c r="M596" s="2"/>
-    </row>
-    <row r="597" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P596" s="2"/>
+    </row>
+    <row r="597" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H597" s="2"/>
       <c r="I597" s="2"/>
       <c r="M597" s="2"/>
-    </row>
-    <row r="598" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P597" s="2"/>
+    </row>
+    <row r="598" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H598" s="2"/>
       <c r="I598" s="2"/>
       <c r="M598" s="2"/>
-    </row>
-    <row r="599" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P598" s="2"/>
+    </row>
+    <row r="599" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H599" s="2"/>
       <c r="I599" s="2"/>
       <c r="M599" s="2"/>
-    </row>
-    <row r="600" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P599" s="2"/>
+    </row>
+    <row r="600" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H600" s="2"/>
       <c r="I600" s="2"/>
       <c r="M600" s="2"/>
+      <c r="P600" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="12">
@@ -3692,7 +4370,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -3701,10 +4379,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3712,7 +4390,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3720,7 +4398,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3728,7 +4406,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3736,7 +4414,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3744,7 +4422,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3752,7 +4430,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3760,7 +4438,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3768,7 +4446,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -3776,7 +4454,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3784,7 +4462,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -3792,7 +4470,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -3800,7 +4478,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -3808,7 +4486,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -3816,7 +4494,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -3824,39 +4502,111 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
